--- a/research/literature-survey/Literature_Extraction.xlsx
+++ b/research/literature-survey/Literature_Extraction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\FraudLens\research\literature-survey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6F1302-11AB-4A9E-AD8E-02945F71FC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFB453E-83FF-437A-87CA-EF83CE41398F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Paper ID</t>
   </si>
@@ -136,6 +136,60 @@
   </si>
   <si>
     <t>http://mdpi.com/2076-3417/12/19/9637</t>
+  </si>
+  <si>
+    <t>P02</t>
+  </si>
+  <si>
+    <t>The Imbalanced Classification of Fraudulent Bank Transactions Using Machine Learning</t>
+  </si>
+  <si>
+    <t>Alexey Ruchay; Elena Feldman; Dmitriy Cherbadzhi; Alexander Sokolov</t>
+  </si>
+  <si>
+    <t>Mathematics, MDPI</t>
+  </si>
+  <si>
+    <t>Detecting fraudulent bank transactions under severe class imbalance</t>
+  </si>
+  <si>
+    <t>To develop and evaluate machine-learning approaches for detecting fraudulent bank transactions and improving classification of the minority fraud class</t>
+  </si>
+  <si>
+    <t>Fraudulent bank/credit-card transactions</t>
+  </si>
+  <si>
+    <t>Data preprocessing; imbalance handling; machine-learning classification; hyperparameter optimization; 10-fold cross-validation</t>
+  </si>
+  <si>
+    <t>Random Forest; TPOT; CatBoost; XGBoost; LightGBM; SVM; KNN; MLP; Decision Tree</t>
+  </si>
+  <si>
+    <t>CreditCardFraud dataset</t>
+  </si>
+  <si>
+    <t>284,807 transactions; 492 fraudulent; 284,315 legitimate</t>
+  </si>
+  <si>
+    <t>Time; Amount; V1–V28 PCA-transformed features; Class label</t>
+  </si>
+  <si>
+    <t>Multiple models achieved high performance; Random Forest reported 0.9999 accuracy, 0.9366 fraud recall and 0.9610 fraud F1</t>
+  </si>
+  <si>
+    <t>The dataset is highly imbalanced and its original feature meanings are unavailable because features are PCA-transformed. The dataset covers only two days of transactions, limiting direct generalization to other financial contexts.</t>
+  </si>
+  <si>
+    <t>Demonstrates the importance of handling class imbalance and evaluating fraud-class Precision, Recall and F1 rather than relying only on Accuracy</t>
+  </si>
+  <si>
+    <t>RQ1; RQ2; RQ3</t>
+  </si>
+  <si>
+    <t>Sections 1, 3.1, 3.2, 4, 5, 6; Table 1; Figure 4</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/math11132862</t>
   </si>
 </sst>
 </file>
@@ -525,11 +579,11 @@
     <col min="11" max="11" width="19.109375" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.21875" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.88671875" style="3" customWidth="1"/>
-    <col min="14" max="14" width="22.109375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="22" style="3" customWidth="1"/>
-    <col min="16" max="16" width="21" style="3" customWidth="1"/>
+    <col min="14" max="14" width="35.6640625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="39.109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="34.5546875" style="3" customWidth="1"/>
     <col min="17" max="17" width="27.33203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="22.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="35" style="1" customWidth="1"/>
     <col min="19" max="19" width="23.6640625" style="1" customWidth="1"/>
     <col min="20" max="16384" width="8.88671875" style="1"/>
   </cols>
@@ -652,26 +706,64 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
+    <row r="3" spans="1:19" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2023</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
@@ -970,7 +1062,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S2" r:id="rId1" xr:uid="{A38B69B3-169A-4791-9FC8-7128EB513ACD}"/>
+    <hyperlink ref="S3" r:id="rId2" xr:uid="{5751E136-023C-4145-B87C-091A39F7EC45}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/research/literature-survey/Literature_Extraction.xlsx
+++ b/research/literature-survey/Literature_Extraction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\FraudLens\research\literature-survey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFB453E-83FF-437A-87CA-EF83CE41398F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F8AE55-84BB-44EB-9EB7-5E5D6D781B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="440">
   <si>
     <t>Paper ID</t>
   </si>
@@ -190,6 +190,1161 @@
   </si>
   <si>
     <t>https://doi.org/10.3390/math11132862</t>
+  </si>
+  <si>
+    <t>P03</t>
+  </si>
+  <si>
+    <t>Financial transaction fraud detector based on imbalance learning and graph neural network</t>
+  </si>
+  <si>
+    <t>Guoxiang Tong; Jieyu Shen</t>
+  </si>
+  <si>
+    <t>Applied Soft Computing, Elsevier</t>
+  </si>
+  <si>
+    <t>Detecting financial fraud in highly imbalanced and complex transaction data while capturing relationships between entities</t>
+  </si>
+  <si>
+    <t>To develop HHLN-GNN for financial transaction fraud detection by addressing category imbalance and exploiting homogeneous and heterogeneous graph connections</t>
+  </si>
+  <si>
+    <t>Financial transaction fraud</t>
+  </si>
+  <si>
+    <t>HHLN-GNN; subgraph generation; neighborhood sampling; graph-based node classification; self-attention</t>
+  </si>
+  <si>
+    <t>Graph Neural Network (GNN); self-attention; subgraph generator; neighborhood sampler</t>
+  </si>
+  <si>
+    <t>YelpChi; Amazon; Elliptic</t>
+  </si>
+  <si>
+    <t>Multiple public benchmark datasets; dataset-specific sizes reported in the paper</t>
+  </si>
+  <si>
+    <t>Graph nodes, edges, node/edge information and transaction-related features</t>
+  </si>
+  <si>
+    <t>Reported improvements over benchmark methods across F1-macro, AUC and GMean; on YelpChi improvements were 10%, 12.5% and 17.3%, and on Amazon 0.7%, 2.5% and 4%, respectively</t>
+  </si>
+  <si>
+    <t>Addresses class imbalance and hidden relational information, but graph construction and dependence on benchmark datasets can affect applicability to other financial environments; specific operational deployment constraints are not established by the study</t>
+  </si>
+  <si>
+    <t>Demonstrates how relationships and graph structure can complement conventional transaction-level fraud detection and is relevant to future entity/network analysis in FraudLens</t>
+  </si>
+  <si>
+    <t>Abstract; Introduction; Datasets; Methodology; Experiments; Conclusion</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.asoc.2023.110984</t>
+  </si>
+  <si>
+    <t>P04</t>
+  </si>
+  <si>
+    <t>Fraud Detection in Financial Transactions: A Machine Learning Approach vs. Rule-Based Systems</t>
+  </si>
+  <si>
+    <t>Arshiya Khanum; Chaitra K S; Brijesh Singh; C Gomathi</t>
+  </si>
+  <si>
+    <t>2024 International Conference on Intelligent and Innovative Technologies in Computing, Electrical and Electronics (IITCEE), IEEE</t>
+  </si>
+  <si>
+    <t>Comparing machine-learning and rule-based approaches for detecting fraudulent financial transactions</t>
+  </si>
+  <si>
+    <t>To investigate the effectiveness of Support Vector Machine (SVM) and Rule-Based Systems (RBS) for financial fraud detection and examine hybrid approaches</t>
+  </si>
+  <si>
+    <t>Comparative evaluation of machine learning and rule-based fraud detection; hybrid approach discussion</t>
+  </si>
+  <si>
+    <t>Support Vector Machine (SVM); Rule-Based System (RBS); hybrid models</t>
+  </si>
+  <si>
+    <t>Financial transaction data; specific dataset details not available in the IEEE abstract</t>
+  </si>
+  <si>
+    <t>Not publicly specified in the IEEE abstract</t>
+  </si>
+  <si>
+    <t>Financial transaction attributes used for fraud detection; specific features not publicly specified in the IEEE abstract</t>
+  </si>
+  <si>
+    <t>ML achieved F1-score 90%, accuracy 95%, precision 92%, recall 89%; ML processing time was 120 ms, while RBS processing time was 50 ms. The paper also discusses hybrid models as a balance between accuracy, efficiency and interpretability.</t>
+  </si>
+  <si>
+    <t>The study reports higher detection performance for ML but greater computational requirements; RBS provides faster processing and interpretability. Detailed dataset and implementation information is not available in the IEEE abstract</t>
+  </si>
+  <si>
+    <t>Useful for comparing traditional rule-based detection with ML and understanding the trade-off between detection performance, computational efficiency and interpretability</t>
+  </si>
+  <si>
+    <t>IEEE Xplore abstract; DOI record</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/IITCEE59897.2024.10467759</t>
+  </si>
+  <si>
+    <t>P05</t>
+  </si>
+  <si>
+    <t>Deep Learning for Credit Card Fraud Detection: A Review of Algorithms, Challenges, and Solutions</t>
+  </si>
+  <si>
+    <t>[Authors as listed in IEEE Xplore]</t>
+  </si>
+  <si>
+    <t>IEEE Access, IEEE</t>
+  </si>
+  <si>
+    <t>Reviewing the use of deep learning for credit-card fraud detection and the challenges associated with applying DL to fraud detection</t>
+  </si>
+  <si>
+    <t>To review recent deep-learning approaches for credit-card fraud detection, compare commonly used architectures, discuss evaluation metrics and identify challenges and possible solutions</t>
+  </si>
+  <si>
+    <t>Credit-card fraud</t>
+  </si>
+  <si>
+    <t>Literature review of deep-learning approaches and experimental analysis using a real-world credit-card fraud dataset</t>
+  </si>
+  <si>
+    <t>CNN; RNN; LSTM; GRU; Artificial Neural Networks</t>
+  </si>
+  <si>
+    <t>Real-world credit-card transaction dataset; exact dataset details should be verified from the full paper</t>
+  </si>
+  <si>
+    <t>Not specified in the publicly available IEEE record</t>
+  </si>
+  <si>
+    <t>Transaction-related features from the real-world credit-card dataset; exact feature list should be verified from the full paper</t>
+  </si>
+  <si>
+    <t>Reviews CNN, RNN, LSTM and GRU approaches and discusses their suitability for credit-card fraud detection, evaluation metrics and common challenges in training DL models</t>
+  </si>
+  <si>
+    <t>Deep-learning fraud detection faces challenges including class imbalance, appropriate evaluation, computational/training requirements and model selection; detailed limitations should be taken from the full paper</t>
+  </si>
+  <si>
+    <t>Provides evidence about deep-learning approaches and their challenges, helping FraudLens evaluate whether DL is applicable beyond conventional ML methods</t>
+  </si>
+  <si>
+    <t>IEEE Xplore abstract and paper; IEEE Access, Volume 12, pp. 96893–96910</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ACCESS.2024.3426955</t>
+  </si>
+  <si>
+    <t>P06</t>
+  </si>
+  <si>
+    <t>Locally Interpretable One-Class Anomaly Detection for Credit Card Fraud Detection</t>
+  </si>
+  <si>
+    <t>Tung-Yu Wu; You-Ting Wang</t>
+  </si>
+  <si>
+    <t>2021 International Conference on Technologies and Applications of Artificial Intelligence (TAAI), IEEE</t>
+  </si>
+  <si>
+    <t>Detecting highly imbalanced credit-card fraud using anomaly detection while providing explanations for model predictions</t>
+  </si>
+  <si>
+    <t>To develop an unsupervised anomaly-detection framework for credit-card fraud and an explanation module for understanding feature contributions</t>
+  </si>
+  <si>
+    <t>Unsupervised adversarial anomaly detection with model explanation</t>
+  </si>
+  <si>
+    <t>AutoEncoder; fully connected discriminator; white-box explainers</t>
+  </si>
+  <si>
+    <t>Benchmark credit-card fraud dataset</t>
+  </si>
+  <si>
+    <t>284,807 transactions; 492 fraudulent transactions</t>
+  </si>
+  <si>
+    <t>Transaction features including anonymized PCA-derived features; exact feature details should be taken from the paper</t>
+  </si>
+  <si>
+    <t>Reported state-of-the-art performance against baseline methods and provided explanations showing how individual features contributed to predictions</t>
+  </si>
+  <si>
+    <t>The study addresses highly imbalanced data and black-box interpretability; the benchmark dataset is anonymized, which limits direct interpretation of individual original financial features</t>
+  </si>
+  <si>
+    <t>Demonstrates that fraud detection can combine unsupervised anomaly detection with explainability, which is relevant to making FraudLens findings more interpretable</t>
+  </si>
+  <si>
+    <t>IEEE Xplore abstract; paper; TAAI 2021, pp. 25–30</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/TAAI54685.2021.00014</t>
+  </si>
+  <si>
+    <t>P07</t>
+  </si>
+  <si>
+    <t>Real-Time Fraud Detection Using Machine Learning</t>
+  </si>
+  <si>
+    <t>Authors: Not verified from publicly accessible IEEE record</t>
+  </si>
+  <si>
+    <t>2025 33rd International Conference on Enabling Technologies: Infrastructure for Collaborative Enterprises (WETICE), IEEE</t>
+  </si>
+  <si>
+    <t>Automating detection of suspicious financial activities in real time under operational constraints faced by financial institutions</t>
+  </si>
+  <si>
+    <t>To develop and evaluate a streaming machine-learning approach for real-time financial transaction monitoring</t>
+  </si>
+  <si>
+    <t>Streaming machine-learning pipeline; real-time transaction monitoring; data-stream processing</t>
+  </si>
+  <si>
+    <t>Machine Learning; streaming ML</t>
+  </si>
+  <si>
+    <t>Financial transaction stream; exact dataset details not publicly specified in the IEEE abstract</t>
+  </si>
+  <si>
+    <t>Not specified in the IEEE abstract</t>
+  </si>
+  <si>
+    <t>Streaming financial transaction data; exact feature set not publicly specified</t>
+  </si>
+  <si>
+    <t>Develops a streaming ML pipeline and experimental testbed designed around real-world constraints including extreme class imbalance, evolving fraud patterns (concept drift), and delayed verified feedback</t>
+  </si>
+  <si>
+    <t>Real-time fraud detection must handle class imbalance, concept drift and delayed feedback; detailed dataset and model implementation information are not publicly specified in the IEEE abstract</t>
+  </si>
+  <si>
+    <t>Introduces real-time and evolving-fraud considerations that are important for evaluating whether FraudLens approaches can support changing transaction behavior and timely analysis</t>
+  </si>
+  <si>
+    <t>IEEE Xplore abstract</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/WETICE67341.2025.11092218</t>
+  </si>
+  <si>
+    <t>P08</t>
+  </si>
+  <si>
+    <t>An intelligent sequential fraud detection model based on deep learning</t>
+  </si>
+  <si>
+    <t>Georgios Zioviris; Kostas Kolomvatsos; George Stamoulis</t>
+  </si>
+  <si>
+    <t>The Journal of Supercomputing, Springer</t>
+  </si>
+  <si>
+    <t>Detecting financial fraud while considering sequential transaction behavior, large transaction volumes, and severe class imbalance</t>
+  </si>
+  <si>
+    <t>To develop a sequential deep-learning fraud detection scheme that combines dimensionality reduction with sequence-based classification and evaluates different oversampling techniques</t>
+  </si>
+  <si>
+    <t>Sequential transaction analysis; dimensionality reduction; temporal/transaction-sequence modeling; oversampling</t>
+  </si>
+  <si>
+    <t>Deep Autoencoder; Variational Autoencoder; LSTM; SMOTE; Borderline-SMOTE; SVM-SMOTE; K-Means SMOTE; ADASYN</t>
+  </si>
+  <si>
+    <t>BankSim synthetic financial transaction dataset</t>
+  </si>
+  <si>
+    <t>594,643 transactions; 587,443 normal and 7,200 fraudulent</t>
+  </si>
+  <si>
+    <t>30 original features; sequential transaction records and transaction-related attributes</t>
+  </si>
+  <si>
+    <t>Best reported model achieved 99.64% AUC with MSE 0.0028 and RMSE 0.0060; the study reports strong recall and precision and compares multiple oversampling techniques</t>
+  </si>
+  <si>
+    <t>BankSim is synthetic; the authors identify incorporation of the temporal axis and seasonality of fraudulent events as future research; results may not directly generalize to real banking data</t>
+  </si>
+  <si>
+    <t>Shows the value of analyzing transaction sequences and historical behavior rather than treating transactions only as independent records; relevant to temporal and behavioral analysis in FraudLens</t>
+  </si>
+  <si>
+    <t>Sections 3–8; especially Sections 4, 5, 7 and 8</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s11227-024-06030-y</t>
+  </si>
+  <si>
+    <t>P09</t>
+  </si>
+  <si>
+    <t>Online payment fraud: from anomaly detection to risk management</t>
+  </si>
+  <si>
+    <t>[Authors as listed in Springer]</t>
+  </si>
+  <si>
+    <t>Financial Innovation, Springer</t>
+  </si>
+  <si>
+    <t>Detecting online payment fraud by identifying deviations from normal customer behavior using behavioral, transactional, and customer-related information</t>
+  </si>
+  <si>
+    <t>To investigate fraud detection from an anomaly-detection and risk-management perspective using deviations from expected customer behavior and combining behavioral, transaction, account, and booking information</t>
+  </si>
+  <si>
+    <t>Online payment fraud / e-banking fraud</t>
+  </si>
+  <si>
+    <t>Behavioral profiling; anomaly detection; historical behavior analysis; session sequence analysis; transaction and customer feature engineering</t>
+  </si>
+  <si>
+    <t>Unsupervised / weakly supervised anomaly detection; feature-based behavioral modeling</t>
+  </si>
+  <si>
+    <t>E-banking/payment transaction data; session and customer behavior data</t>
+  </si>
+  <si>
+    <t>Exact dataset size not stated in the article's highlighted methodology</t>
+  </si>
+  <si>
+    <t>Behavioral session features, transaction features, customer/account information, booking information, timestamps and request sequences</t>
+  </si>
+  <si>
+    <t>The study shows that combining behavioral, transactional, customer-related and account information can improve fraud detection; behavioral features capture deviations from a customer's normal interaction patterns</t>
+  </si>
+  <si>
+    <t>Real-world payment fraud involves large transaction volumes, severe class imbalance, dynamic fraud behavior, limited forensic information and varying customer behavior; the approach depends on historical behavioral data and feature engineering</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it demonstrates that investigation-oriented transaction analysis should consider historical behavior and deviations from normal patterns, rather than relying only on isolated transaction attributes</t>
+  </si>
+  <si>
+    <t>Sections on data, behavioral features, transactional features, customer-related features and anomaly detection</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s40854-023-00470-w</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>Dynamic quantification anti-fraud machine learning model for real-time transaction fraud detection in banking</t>
+  </si>
+  <si>
+    <t>Falai Li; Zaidie Chen</t>
+  </si>
+  <si>
+    <t>Discover Computing, Springer</t>
+  </si>
+  <si>
+    <t>Real-time detection of suspicious banking transactions using historical transaction patterns and dynamically weighted fraud indicators</t>
+  </si>
+  <si>
+    <t>To develop a dynamic anti-fraud model that quantifies multiple transaction-risk indicators and performs instantaneous risk assessment for bank accounts</t>
+  </si>
+  <si>
+    <t>Banking / telecom-related financial fraud</t>
+  </si>
+  <si>
+    <t>Real-time transaction monitoring; historical behavior analysis; transaction frequency; rapid consecutive transactions; transaction amount; transaction timing; unfamiliar counterparties; geographic anomalies</t>
+  </si>
+  <si>
+    <t>Dynamic Quantification Anti-Fraud Model; Double Machine Learning (DML); LightGBM; XGBoost; expert-rule features</t>
+  </si>
+  <si>
+    <t>Transaction detail data from Agricultural Bank of China, Zhejiang Branch; implicated-card data from January 2022 to June 2023</t>
+  </si>
+  <si>
+    <t>633 positive test samples; training/validation sizes not disclosed</t>
+  </si>
+  <si>
+    <t>Transaction amount; transaction frequency; transaction time; unfamiliar counterparty; geographic location; rapid consecutive transactions; small-amount tests; other expert-defined behavioral indicators</t>
+  </si>
+  <si>
+    <t>Validation sample recall reached 0.506; after deployment, the proportion of implicated cards decreased by 30 percentage points over six months at the bank</t>
+  </si>
+  <si>
+    <t>Training/control data selection is not fully representative of real-world fraud prevalence; training and validation dataset sizes were not disclosed; the model relies partly on expert-defined indicators and bank-specific operational thresholds</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it demonstrates how historical transaction behavior, frequency, timing, counterparties and rapid transaction sequences can be combined for real-time risk analysis</t>
+  </si>
+  <si>
+    <t>Sections 1, 2, 2.1, 2.2; especially lines describing historical transaction patterns, frequent transfers and rapid consecutive transactions</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10791-025-09549-7</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>Fraud detection with natural language processing</t>
+  </si>
+  <si>
+    <t>Petros Boulieris; John Pavlopoulos; Alexandros Xenos; Vasilis Vassalos</t>
+  </si>
+  <si>
+    <t>Machine Learning, Springer</t>
+  </si>
+  <si>
+    <t>Detection of fraud in online and mobile banking by analyzing sequences of user actions preceding transactions</t>
+  </si>
+  <si>
+    <t>To investigate whether sequences of online banking actions can be used as predictive features for fraud detection with limited manual feature engineering</t>
+  </si>
+  <si>
+    <t>Online / Mobile Banking Fraud</t>
+  </si>
+  <si>
+    <t>User action sequences; transaction history; temporal ordering; API calls; login/logout; balance checks; payment actions; action frequency and n-grams</t>
+  </si>
+  <si>
+    <t>FraudNLP; TF-IDF; n-gram features; Logistic Regression; Random Forest; kNN; SVM; LSTM; CNN; TCN; Isolation Forest</t>
+  </si>
+  <si>
+    <t>Anonymized online and mobile banking data from a European bank</t>
+  </si>
+  <si>
+    <t>105,303 transactions from 2,000 users; 101 confirmed fraudulent transactions (0.096%)</t>
+  </si>
+  <si>
+    <t>User actions; timestamps; transaction amount; elapsed time; API calls; application type; device characteristics; operating system; IP address; RFM features; action n-grams; anomaly scores</t>
+  </si>
+  <si>
+    <t>Sequence-based NLP features improved fraud classification compared with conventional RFM features; the combined RFM + NLP approach achieved strong performance, while LSTM achieved the highest F2 score of 0.522 in the reported combined-feature experiments</t>
+  </si>
+  <si>
+    <t>Very severe class imbalance; only 101 confirmed fraud transactions; anonymization removed identifiers, detailed timestamps, GPS, account balances and other potentially useful information; unlabeled fraud may remain; results depend on the specific banking action logs available</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because transaction investigation can incorporate preceding user actions and temporal sequences rather than treating each transaction as an isolated record; also supports behavioral and anomaly-based feature design</t>
+  </si>
+  <si>
+    <t>RQ1; RQ2; RQ3; RQ4; RQ5</t>
+  </si>
+  <si>
+    <t>Sections 1, 3.1, 3.1.3, 4.3–4.6; especially the FraudNLP dataset and action-sequence methodology</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10994-023-06354-5</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>SMoTeF: Smurf money laundering detection using temporal order and flow analysis</t>
+  </si>
+  <si>
+    <t>Shiva Shadrooh; Kjetil Nørvåg</t>
+  </si>
+  <si>
+    <t>Applied Intelligence, Springer</t>
+  </si>
+  <si>
+    <t>Detection of smurfing money-laundering patterns by considering transaction temporal order and the flow of money through intermediary accounts</t>
+  </si>
+  <si>
+    <t>To reduce false-positive smurfing patterns by incorporating temporal ordering and maximum temporal flow into graph-based fraud detection</t>
+  </si>
+  <si>
+    <t>Smurfing / Money Laundering</t>
+  </si>
+  <si>
+    <t>Temporal transaction order; recurring transactions; intermediary accounts; money-flow volume; suspicious activity periods; transaction sequences; fund-flow patterns</t>
+  </si>
+  <si>
+    <t>SMoTeF; temporal graph analysis; maximum temporal flow; temporal-order constraints; graph-based pattern detection; AA-SMURF baseline</t>
+  </si>
+  <si>
+    <t>Three real-world datasets from different domains; CFD with injected smurfing patterns, DARPA intrusion dataset, and Enron email dataset</t>
+  </si>
+  <si>
+    <t>DARPA: 4.5M IP-IP communications; Enron: 500K+ emails; CFD uses injected smurfing patterns with 5–50 intermediaries</t>
+  </si>
+  <si>
+    <t>Transaction timestamps; transaction/edge amounts; source and destination accounts; intermediary nodes; temporal order; money-flow volume</t>
+  </si>
+  <si>
+    <t>SMoTeF significantly reduced false-positive patterns compared with the AA-SMURF baseline and identified the most suspicious activity periods for detected patterns</t>
+  </si>
+  <si>
+    <t>Does not directly evaluate long chains of layered smurfing; flow and smurf thresholds depend on domain-specific knowledge and may introduce variability; CFD fraud patterns are injected rather than naturally occurring</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it supports temporal fund-flow tracing, identification of intermediary accounts, suspicious activity periods, and evidence-based investigation of transaction networks</t>
+  </si>
+  <si>
+    <t>Sections 1, 3.1–3.2, 4, 5.1, 5.6 and 6; especially the temporal-order and maximum-temporal-flow methodology</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10489-024-05545-4</t>
+  </si>
+  <si>
+    <t>P13</t>
+  </si>
+  <si>
+    <t>Enhancing financial fraud detection with graph neural network and ensemble learning: insights from Related Party Transactions network</t>
+  </si>
+  <si>
+    <t>Xuting Mao; Jianping Li; Xiaoqian Zhu; Yinghui Wang</t>
+  </si>
+  <si>
+    <t>International Review of Economics &amp; Finance, Elsevier</t>
+  </si>
+  <si>
+    <t>Financial fraud detection using related-party transaction networks and higher-order relationships between firms and individuals</t>
+  </si>
+  <si>
+    <t>To incorporate related-party relationships and higher-order network structures into financial fraud detection and combine graph-derived interaction features with conventional financial indicators</t>
+  </si>
+  <si>
+    <t>Corporate / Financial Statement Fraud</t>
+  </si>
+  <si>
+    <t>Related-party transactions; company relationships; related individuals; cross-entity interactions; higher-order network structures; relational transaction patterns; firm-level financial indicators</t>
+  </si>
+  <si>
+    <t>Graph Neural Network; multi-relational Related Party Transactions network; stacking ensemble learning; structure-aware representation</t>
+  </si>
+  <si>
+    <t>Financial and related-party transaction data covering listed companies and their related entities</t>
+  </si>
+  <si>
+    <t>3,793 listed companies; 68,571 related companies; 6,072 related individuals</t>
+  </si>
+  <si>
+    <t>Financial indicators; related-party transaction relationships; company-to-company relationships; company-to-individual relationships; higher-order network features; GNN-derived interaction features</t>
+  </si>
+  <si>
+    <t>Including related-party transaction information increased AUC by 1.67% compared with financial data alone; incorporating structure-aware representations increased AUC by a further 3.04%</t>
+  </si>
+  <si>
+    <t>Results are based on listed-company related-party transaction networks; data availability is on request; applicability may depend on the availability and quality of relationship data</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it provides research support for modelling companies, individuals and transactions as interconnected entities and using relationship structure as an additional fraud signal</t>
+  </si>
+  <si>
+    <t>RQ1; RQ2; RQ4; RQ5</t>
+  </si>
+  <si>
+    <t>Abstract; Introduction; methodology describing the multi-relational RPT network and GNN-based interaction features; empirical results</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.iref.2026.105217</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>Detecting Financial Fraud and Anomalies in Corporate Transactions with Convolutional Neural Networks</t>
+  </si>
+  <si>
+    <t>Authors as listed in Springer</t>
+  </si>
+  <si>
+    <t>International Journal of Computational Intelligence Systems, Springer</t>
+  </si>
+  <si>
+    <t>Detection of financial fraud by modelling accounts and transactions as a temporal directed weighted graph and learning relational and topological patterns</t>
+  </si>
+  <si>
+    <t>To investigate whether graph-based representations of corporate transactions can capture relational and structural patterns associated with financial fraud</t>
+  </si>
+  <si>
+    <t>Financial Transaction Fraud / Corporate Fraud</t>
+  </si>
+  <si>
+    <t>Transaction networks; sender-receiver relationships; temporal transaction structure; transaction amount; transaction type; graph topology; account relationships</t>
+  </si>
+  <si>
+    <t>Graph Convolutional Network; Convolutional Neural Network; temporal directed weighted graph</t>
+  </si>
+  <si>
+    <t>PaySim financial transaction dataset</t>
+  </si>
+  <si>
+    <t>Not publicly specified in the accessible article record</t>
+  </si>
+  <si>
+    <t>Source account; destination account; transaction amount; transaction type; timestamp; graph connectivity and topology</t>
+  </si>
+  <si>
+    <t>Graph representation enables the model to capture relational and topological fraud patterns that are difficult to represent using isolated transaction features</t>
+  </si>
+  <si>
+    <t>Uses a synthetic financial transaction dataset; generalization to real institutional transaction networks requires further validation; detailed operational investigation capabilities are outside the study scope</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it provides evidence for representing accounts as graph nodes and transactions as directed edges, supporting relationship analysis, network-based anomaly detection and future fund-flow investigation</t>
+  </si>
+  <si>
+    <t>Sections describing graph construction and temporal directed weighted transaction network; especially the graph representation of sender-receiver accounts and transaction attributes</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s44196-026-01275-2</t>
+  </si>
+  <si>
+    <t>P15</t>
+  </si>
+  <si>
+    <t>GraphSIF: analyzing flow of payments in a Business-to-Business network to detect supplier impersonation</t>
+  </si>
+  <si>
+    <t>Applied Network Science, Springer</t>
+  </si>
+  <si>
+    <t>Supplier impersonation fraud detection through analysis of payment relationships between a company and its suppliers</t>
+  </si>
+  <si>
+    <t>To use the structure of a company's supplier transaction network to identify suspicious payment transactions and distinguish fraudulent supplier relationships from legitimate ones</t>
+  </si>
+  <si>
+    <t>Supplier Impersonation / Business-to-Business Fraud</t>
+  </si>
+  <si>
+    <t>Company-supplier relationships; payment flows; transaction similarity; supplier networks; historical transaction patterns; network structure</t>
+  </si>
+  <si>
+    <t>Self-Organizing Map; graph-based anomaly detection; transaction-network analysis</t>
+  </si>
+  <si>
+    <t>SIS-ID real-world B2B transaction dataset</t>
+  </si>
+  <si>
+    <t>Exact dataset size not publicly specified in the accessible article record</t>
+  </si>
+  <si>
+    <t>Payment amount; supplier identity; transaction relationships; historical transaction behavior; network structure; transaction similarity</t>
+  </si>
+  <si>
+    <t>Experiments showed high consistency with expert knowledge on a real-life dataset and faster processing than the expert system used for comparison</t>
+  </si>
+  <si>
+    <t>Focused on the specific supplier-impersonation scenario; generalization to other fraud types requires further evaluation; detailed dataset characteristics are not publicly specified</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it demonstrates how transaction relationships and historical payment networks can support investigation of suspicious entities, especially supplier/company relationships</t>
+  </si>
+  <si>
+    <t>Abstract; Introduction; methodology describing the supplier transaction network and graph-based anomaly detection; experimental evaluation</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s41109-020-00283-1</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>Finding money launderers using heterogeneous graph neural networks</t>
+  </si>
+  <si>
+    <t>Authors as listed in ScienceDirect</t>
+  </si>
+  <si>
+    <t>The Journal of Finance and Data Science, Elsevier</t>
+  </si>
+  <si>
+    <t>Detection of money laundering using a heterogeneous graph constructed from real-world bank transactions and business-role information</t>
+  </si>
+  <si>
+    <t>To investigate whether heterogeneous graph neural networks can identify money-laundering activities by jointly modelling financial transactions and different types of business entities and relationships</t>
+  </si>
+  <si>
+    <t>Money Laundering / AML</t>
+  </si>
+  <si>
+    <t>Bank transactions; customer relationships; business roles; heterogeneous entities; transaction networks; relational structure; entity types</t>
+  </si>
+  <si>
+    <t>Heterogeneous Graph Neural Network; Message Passing Neural Network; heterogeneous message passing; PyTorch Geometric</t>
+  </si>
+  <si>
+    <t>Real-world transaction and business-role data from DNB, Norway's largest bank</t>
+  </si>
+  <si>
+    <t>Transaction relationships; entity types; business roles; account/customer relationships; graph connectivity; historical transaction information</t>
+  </si>
+  <si>
+    <t>Reports that the heterogeneous GNN approach can identify money-laundering activity in a large real-world heterogeneous financial network and demonstrates the suitability of heterogeneous GNNs for electronic surveillance</t>
+  </si>
+  <si>
+    <t>Specific dataset and institutional context may limit direct generalization; detailed operational data and some dataset characteristics are not publicly disclosed</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it supports modelling different entity types and relationships together, providing research evidence for a heterogeneous Knowledge Graph / investigation graph rather than a transaction-only graph</t>
+  </si>
+  <si>
+    <t>Abstract; methodology describing the heterogeneous financial network and heterogeneous MPNN; experimental evaluation</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jfds.2025.100175</t>
+  </si>
+  <si>
+    <t>P17</t>
+  </si>
+  <si>
+    <t>FlowSeries: flow analysis on financial networks</t>
+  </si>
+  <si>
+    <t>Arthur Capozzi; Salvatore Vilella; Dario Moncalvo; Marco Fornasiero; Valeria Ricci; Silvia Ronchiadin; Giancarlo Ruffo</t>
+  </si>
+  <si>
+    <t>Top-down analysis of financial transaction networks to identify anomalous transaction flows and suspicious actors for anti-financial-crime investigations</t>
+  </si>
+  <si>
+    <t>To develop an interpretable and scalable flow-analysis methodology that helps anti-financial-crime analysts explore complex transaction patterns without relying on predefined fraud patterns or large labelled training datasets</t>
+  </si>
+  <si>
+    <t>Financial Crime / Anti-Money Laundering</t>
+  </si>
+  <si>
+    <t>Cross-border transactions; payment paths; intermediary entities; temporal transaction networks; transaction-flow weights; recurring patterns; anomalous flows; direct versus indirect transfers</t>
+  </si>
+  <si>
+    <t>FlowSeries; weighted directed temporal graphs; depth-first search; maximum-flow-inspired transaction-flow analysis; moving-average anomaly analysis</t>
+  </si>
+  <si>
+    <t>Real-world anonymized cross-border banking transactions provided by Intesa Sanpaolo</t>
+  </si>
+  <si>
+    <t>80 million transactions over 15 months</t>
+  </si>
+  <si>
+    <t>IBAN; BIC; country; transaction timestamp; transaction amount; directed payment relationships; temporal aggregation; intermediary paths</t>
+  </si>
+  <si>
+    <t>FlowSeries supported AFC analysts in identifying anomalous transaction flows and suspicious actors, scaled to millions of transactions, and provided interpretable outputs that could support formal investigation</t>
+  </si>
+  <si>
+    <t>FlowSeries relies on analyst-selected starting points and interpretation; path exploration can become computationally expensive in highly connected networks; temporal aggregation is an approximation; data are anonymized and access is restricted</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it directly demonstrates an interpretable investigator-support workflow for tracing multi-hop fund flows, identifying suspicious entities and analysing changes in transaction relationships over time</t>
+  </si>
+  <si>
+    <t>Sections 1, 2, 3 and 5; especially the transaction-network model, FlowSeries methodology and real-world AFC case studies</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s41109-025-00711-0</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>An analysis of one-to-one matching algorithms for entity resolution</t>
+  </si>
+  <si>
+    <t>George Papadakis; Vasilis Efthymiou; Emmanouil Thanos; Oktie Hassanzadeh; Peter Christen; et al.</t>
+  </si>
+  <si>
+    <t>The VLDB Journal, Springer</t>
+  </si>
+  <si>
+    <t>Entity resolution across structured datasets by matching records that refer to the same real-world entities</t>
+  </si>
+  <si>
+    <t>To empirically evaluate one-to-one entity-resolution matching algorithms with respect to matching quality and computational efficiency</t>
+  </si>
+  <si>
+    <t>Entity Resolution / Record Linkage</t>
+  </si>
+  <si>
+    <t>Bipartite record matching; duplicate detection; similarity graphs; record linkage; entity matching; blocking; one-to-one matching</t>
+  </si>
+  <si>
+    <t>Maximum Weight Matching; Greedy Matching; Stable Marriage; Hungarian Algorithm; other bipartite graph matching algorithms</t>
+  </si>
+  <si>
+    <t>10 established real-world datasets used to construct more than 700 similarity graphs</t>
+  </si>
+  <si>
+    <t>10 datasets; more than 700 generated similarity graphs</t>
+  </si>
+  <si>
+    <t>Record attributes; pairwise similarities; candidate pairs; similarity graphs; source-specific entity records</t>
+  </si>
+  <si>
+    <t>Provides a systematic empirical comparison of eight bipartite graph matching algorithms and analyzes the trade-off between matching accuracy and execution time</t>
+  </si>
+  <si>
+    <t>Focuses on general entity-resolution datasets rather than financial-fraud-specific data; performance varies by dataset characteristics and similarity-graph structure</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because investigation data from documents, transactions and external records may contain duplicate or inconsistent representations of the same person, company or account; entity resolution can therefore improve the reliability of the investigation graph</t>
+  </si>
+  <si>
+    <t>RQ2; RQ3; RQ4; RQ5</t>
+  </si>
+  <si>
+    <t>Abstract; Sections describing Clean-Clean Entity Resolution, bipartite similarity graphs, matching algorithms and experimental evaluation</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s00778-023-00791-3</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>Artificial intelligence for knowledge graphs of cryptocurrency anti-money laundering in fintech</t>
+  </si>
+  <si>
+    <t>Min-Yuh Day</t>
+  </si>
+  <si>
+    <t>Proceedings of the 2021 IEEE/ACM International Conference on Advances in Social Networks Analysis and Mining (ASONAM)</t>
+  </si>
+  <si>
+    <t>Construction of a cryptocurrency anti-money-laundering knowledge graph from legal cases and judgments to represent relationships between crime patterns and financial technologies</t>
+  </si>
+  <si>
+    <t>To use AI and few-shot/meta-learning techniques to construct a knowledge graph for cryptocurrency anti-money-laundering analysis and support analysis and question answering over legal documents</t>
+  </si>
+  <si>
+    <t>Cryptocurrency Money Laundering / Financial Crime</t>
+  </si>
+  <si>
+    <t>Legal cases; judgments; crime patterns; cryptocurrency; electronic payment tools; financial amounts; crime types; temporal trends; entity relationships</t>
+  </si>
+  <si>
+    <t>AI meta-learning; few-shot learning; knowledge graph construction; content analysis; knowledge-based question answering</t>
+  </si>
+  <si>
+    <t>Small-sample international cryptocurrency money-laundering cases and legal judgments</t>
+  </si>
+  <si>
+    <t>Small sample; exact number of cases not specified in the accessible record</t>
+  </si>
+  <si>
+    <t>Case entities; crime types; financial amounts; background/context; growth trends; relationships extracted from legal documents</t>
+  </si>
+  <si>
+    <t>Proposes an AI-based approach for constructing an AML knowledge graph from limited legal-case material and identifies applications in legal-document content analysis and question answering</t>
+  </si>
+  <si>
+    <t>Focused on cryptocurrency AML and a small sample of international cases; exact dataset size and detailed extraction/evaluation statistics are not publicly specified in the accessible record</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it demonstrates how investigation-related documents and case knowledge can be converted into a structured knowledge graph and subsequently used for document analysis and question answering</t>
+  </si>
+  <si>
+    <t>Abstract and paper description covering AI-based cryptocurrency AML knowledge-graph construction, legal-case analysis and question-answering applications</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3487351.3488415</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>Financial fraud detection model based on dual-layer knowledge graph</t>
+  </si>
+  <si>
+    <t>Ying Jiang</t>
+  </si>
+  <si>
+    <t>Discover Artificial Intelligence, Springer</t>
+  </si>
+  <si>
+    <t>Financial fraud detection through a dual-layer knowledge graph combining enterprise financial semantics, inter-enterprise relationships, path mining and explicit fraud rules</t>
+  </si>
+  <si>
+    <t>To establish a unified representation and reasoning mechanism connecting financial indicators, enterprise relationships and cross-layer paths for interpretable financial fraud detection</t>
+  </si>
+  <si>
+    <t>Corporate Financial Fraud / Financial Statement Fraud</t>
+  </si>
+  <si>
+    <t>Financial indicators; accounting dependencies; enterprise relationships; organizational structures; cross-enterprise paths; semantic relationships; fraud rules</t>
+  </si>
+  <si>
+    <t>Dual-Layer Knowledge Graph (DLKG); cross-layer path mining; rule-vector discrimination; XGBoost; Graph Attention Network; R-GCN; Hetero-GNN</t>
+  </si>
+  <si>
+    <t>Enterprise financial and organizational relationship data; sample of enterprises used for evaluation</t>
+  </si>
+  <si>
+    <t>700 enterprises in the reported evaluation</t>
+  </si>
+  <si>
+    <t>Financial indicators; accounting relationships; enterprise relationships; organizational structures; entity mappings; graph paths</t>
+  </si>
+  <si>
+    <t>Reported accuracy of 94.2%, precision 92.7%, recall 93.5%, F1 93.1% and AUC 0.95 on the reported 700-enterprise sample; cross-layer path mining converts structural relationships into explicit fraud rules</t>
+  </si>
+  <si>
+    <t>Focused on corporate financial fraud and enterprise-level data; performance and applicability outside the studied enterprise/financial-statement context require further validation; the reported results depend on the constructed knowledge graph and rule-mining process</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it demonstrates how graph relationships can be converted into explicit, traceable fraud patterns rather than producing only an opaque risk score; supports evidence-oriented reasoning and investigator review</t>
+  </si>
+  <si>
+    <t>Abstract; Introduction; methodology on the dual-layer knowledge graph, cross-layer path mining and rule-vector discrimination; experimental evaluation</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s44163-026-02097-z</t>
+  </si>
+  <si>
+    <t>P21</t>
+  </si>
+  <si>
+    <t>Semi-supervised Credit Card Fraud Detection via Attribute-Driven Graph Representation</t>
+  </si>
+  <si>
+    <t>Sheng Xiang; Mingzhi Zhu; Dawei Cheng; Enxia Li; Ruihui Zhao; Yi Ouyang; Ling Chen; Yefeng Zheng</t>
+  </si>
+  <si>
+    <t>Proceedings of the AAAI Conference on Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Detection of credit-card fraud by modelling temporal relationships among transactions and propagating fraud-risk information through the transaction graph</t>
+  </si>
+  <si>
+    <t>To exploit large amounts of unlabeled transaction data and model fraud patterns through temporal graph representation and risk propagation</t>
+  </si>
+  <si>
+    <t>Credit Card Fraud</t>
+  </si>
+  <si>
+    <t>Temporal transaction relationships; transaction attributes; neighboring transactions; fraud-risk propagation; unlabeled transactions; temporal dependencies</t>
+  </si>
+  <si>
+    <t>Gated Temporal Attention Network (GTAN); semi-supervised graph neural network; temporal graph representation; risk propagation</t>
+  </si>
+  <si>
+    <t>One real-world transaction dataset and two publicly available fraud-detection datasets</t>
+  </si>
+  <si>
+    <t>Exact size of the real-world dataset is not specified in the accessible paper record</t>
+  </si>
+  <si>
+    <t>Transaction attributes; temporal information; transaction interactions; graph topology; labeled and unlabeled transaction data</t>
+  </si>
+  <si>
+    <t>Reported that GTAN outperformed state-of-the-art baselines on three fraud-detection datasets; semi-supervised experiments showed strong performance with only a small proportion of labeled transactions</t>
+  </si>
+  <si>
+    <t>Exact dataset characteristics and full numerical results are not available from the accessible public record; approach is primarily evaluated for credit-card transaction fraud</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it provides research evidence for propagating fraud-risk information through connected transactions, helping identify hidden fraud patterns that may not be visible from an isolated transaction</t>
+  </si>
+  <si>
+    <t>Abstract and methodology describing temporal transaction-graph construction, Gated Temporal Attention Network and risk propagation</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1609/aaai.v37i12.26792</t>
+  </si>
+  <si>
+    <t>P22</t>
+  </si>
+  <si>
+    <t>Explainable fraud detection of financial statement data driven by two-layer knowledge graph</t>
+  </si>
+  <si>
+    <t>Siqi Cai; Zhenping Xie</t>
+  </si>
+  <si>
+    <t>Expert Systems with Applications, Elsevier</t>
+  </si>
+  <si>
+    <t>Explainable financial statement fraud detection by modelling financial-variable relationships in a two-layer knowledge graph and mining fraudulent patterns</t>
+  </si>
+  <si>
+    <t>To construct an explainable fraud detection method capable of extracting fraudulent patterns and providing credible fraud assertions</t>
+  </si>
+  <si>
+    <t>Financial Statement Fraud</t>
+  </si>
+  <si>
+    <t>Financial variables; financial ratios; semantic relationships; syntactic/articulation relationships; financial statement structure; fraudulent patterns</t>
+  </si>
+  <si>
+    <t>Two-Layer Knowledge Graph (FSFD-TLKG); fraudulent pattern mining; adaptive credible assertion; machine learning classification</t>
+  </si>
+  <si>
+    <t>Financial statements of listed companies from China Stock Market &amp; Accounting Research Database (CSMAR); fraud labels from China Securities Regulatory Commission administrative penalty decisions</t>
+  </si>
+  <si>
+    <t>74 listed companies, 2009–2022</t>
+  </si>
+  <si>
+    <t>Financial statement variables; derived financial ratios; semantic relationships among variables; articulation relationships between financial statements; fraud labels</t>
+  </si>
+  <si>
+    <t>FSFD-TLKG extracted explainable fraudulent patterns and achieved better detection performance than most traditional ML and deep-learning methods reported in the study; extracted explainable patterns also improved XGBoost performance</t>
+  </si>
+  <si>
+    <t>Focused on financial-statement fraud rather than transaction-level or AML investigation; dataset covers a limited set of listed companies; applicability to transaction networks and investigative evidence requires further validation</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it demonstrates how knowledge-graph relationships can be converted into explicit fraudulent patterns, supporting explainable findings rather than unexplained fraud probabilities</t>
+  </si>
+  <si>
+    <t>Abstract; Knowledge-graph construction; fraudulent-pattern mining; experimental setup and conclusion</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.eswa.2023.123126</t>
+  </si>
+  <si>
+    <t>P23</t>
+  </si>
+  <si>
+    <t>Information Extraction from Text Intensive and Visually Rich Banking Documents</t>
+  </si>
+  <si>
+    <t>Berke Oral; Erdem Emekligil; Seçil Arslan; Gülşen Eryiǧit</t>
+  </si>
+  <si>
+    <t>Information Processing &amp; Management, Elsevier</t>
+  </si>
+  <si>
+    <t>Information extraction from scanned banking documents by jointly analysing textual content and document layout</t>
+  </si>
+  <si>
+    <t>To automate information extraction from banking documents while reducing manual document classification, data-entry and validation workload</t>
+  </si>
+  <si>
+    <t>Banking Documents / Money Transfer Orders</t>
+  </si>
+  <si>
+    <t>Document images; OCR text; document layout; named entities; complex relations; tables and visual structure; cross-media information</t>
+  </si>
+  <si>
+    <t>OCR; Natural Language Processing; Named Entity Recognition; deep learning; graph-based relation extraction; document-layout analysis</t>
+  </si>
+  <si>
+    <t>Real-world scanned banking money-transfer orders</t>
+  </si>
+  <si>
+    <t>Exact dataset size not publicly specified in the accessible record</t>
+  </si>
+  <si>
+    <t>OCR-extracted text; document images; layout information; entities; relations; visual and textual features</t>
+  </si>
+  <si>
+    <t>Combining textual and visual/layout information improved information-extraction performance; the system successfully extracted complex n-ary, nested and document-level relations from banking documents</t>
+  </si>
+  <si>
+    <t>Focused on banking money-transfer orders; human validation/approval remained necessary; exact dataset size and some operational details are not publicly specified</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because investigation documents may be scanned PDFs containing tables, forms, signatures and visually structured information; supports an OCR + document-layout + information-extraction pipeline before evidence is indexed or linked to transactions/entities</t>
+  </si>
+  <si>
+    <t>Abstract; methodology describing OCR, document understanding, named-entity extraction, complex relation extraction and document-layout information</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ipm.2021.102559</t>
+  </si>
+  <si>
+    <t>P24</t>
+  </si>
+  <si>
+    <t>Defining the problem: The impact of OCR quality on retrieval-augmented generation performance and strategies for improvement</t>
+  </si>
+  <si>
+    <t>Investigating how OCR quality and document structure affect retrieval-augmented generation over image-based financial documents</t>
+  </si>
+  <si>
+    <t>To evaluate the downstream impact of OCR errors on chunking, embedding, retrieval and generation in RAG systems and investigate structured representations as a way to improve retrieval</t>
+  </si>
+  <si>
+    <t>Financial Services Documents / Banking and Insurance Documents</t>
+  </si>
+  <si>
+    <t>OCR text; scanned financial documents; document layout; numerical values; bilingual text; tables; key-value pairs; document structure; evidence-supported QA</t>
+  </si>
+  <si>
+    <t>OCR; RAG; semantic retrieval; document chunking; embeddings; structured tabular representation</t>
+  </si>
+  <si>
+    <t>AI-Hub Korean financial document image dataset containing annotated financial document images and key-value information; additional real-world banking and insurance document images</t>
+  </si>
+  <si>
+    <t>Exact full dataset size not publicly specified in the accessible article record</t>
+  </si>
+  <si>
+    <t>OCR text; bounding boxes; transcribed text; language information; document layout; structured key-value data; ground-truth evidence</t>
+  </si>
+  <si>
+    <t>High-quality OCR alone did not consistently produce strong RAG performance; converting OCR output into structured tabular representations substantially improved generative-AI accuracy, reduced unanswerable responses and reduced the number of chunks required for retrieval</t>
+  </si>
+  <si>
+    <t>Primarily evaluated Korean and English financial documents; effectiveness under poor OCR quality and broader multilingual settings remains uncertain; structured-table transformation is most applicable to documents with relatively concise information</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it demonstrates that document processing cannot stop at OCR; preserving layout and structure before RAG retrieval can improve evidence retrieval and reduce context fragmentation</t>
+  </si>
+  <si>
+    <t>Abstract; dataset description; experiments evaluating OCR, chunking, retrieval and generation; conclusions on structured OCR representation</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ipm.2025.104183</t>
+  </si>
+  <si>
+    <t>P25</t>
+  </si>
+  <si>
+    <t>Addressing investor concerns: a Chinese financial question-answering benchmark with LLM-based evaluation</t>
+  </si>
+  <si>
+    <t>Yunfei Gan; Yutao Tao; Jia Mo; et al.</t>
+  </si>
+  <si>
+    <t>EPJ Data Science, Springer</t>
+  </si>
+  <si>
+    <t>Financial question answering and evidence retrieval over long, complex annual reports containing text, tables and numerical information</t>
+  </si>
+  <si>
+    <t>To create a realistic benchmark for financial-report information retrieval and question answering and evaluate whether current retrieval and LLM-based approaches can produce answers grounded in financial documents</t>
+  </si>
+  <si>
+    <t>Financial Reports / Financial Analysis</t>
+  </si>
+  <si>
+    <t>Multi-page PDFs; tables; textual content; numerical information; page-level evidence; cross-page reasoning; document retrieval; financial questions</t>
+  </si>
+  <si>
+    <t>Financial Information Retrieval; Financial Question Answering; BM25; BGE-M3; BGE-Reranker-v2-m3; RAG; LLM-based evaluation</t>
+  </si>
+  <si>
+    <t>Annual reports of publicly listed Chinese companies combined with real investor questions from the China Investor Forum</t>
+  </si>
+  <si>
+    <t>516 annual reports; 13,643 investor questions covering 2019–2022</t>
+  </si>
+  <si>
+    <t>Financial report text; tables; numerical values; question-answer pairs; report pages; company/year metadata</t>
+  </si>
+  <si>
+    <t>Benchmark analysis found retrieval quality to be a major bottleneck; BM25 consistently outperformed dense and hybrid retrieval methods across the reported retrieval metrics; dataset supports page-level evidence retrieval and grounded financial QA</t>
+  </si>
+  <si>
+    <t>Focused on Chinese financial reports and investor questions; 2,065 questions had no answer located in the report and 1,000 were associated with unavailable reports; findings may not directly generalize to other document types or languages</t>
+  </si>
+  <si>
+    <t>Highly relevant to FraudLens because it supports page-level evidence retrieval and document-grounded question answering over long financial PDFs, helping an investigator trace an AI answer back to the source document</t>
+  </si>
+  <si>
+    <t>Sections 1, 3, 4, 7.1.2 and 8; especially dataset construction, Financial Information Retrieval, Financial QA and retrieval-baseline evaluation</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1140/epjds/s13688-025-00601-6</t>
   </si>
 </sst>
 </file>
@@ -262,7 +1417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -280,6 +1435,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -563,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" style="1" customWidth="1"/>
@@ -765,306 +1923,1392 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
+    <row r="4" spans="1:19" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4">
+        <v>2023</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
+    <row r="5" spans="1:19" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
+    <row r="6" spans="1:19" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S6" s="6" t="s">
+        <v>104</v>
+      </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
+    <row r="7" spans="1:19" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="4">
+        <v>2021</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
+    <row r="8" spans="1:19" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
+    <row r="9" spans="1:19" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
+    <row r="10" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2023</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>169</v>
+      </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
+    <row r="11" spans="1:19" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2025</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>186</v>
+      </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
+    <row r="12" spans="1:19" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2023</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>204</v>
+      </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
+    <row r="13" spans="1:19" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2024</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="P13" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="S13" s="6" t="s">
+        <v>221</v>
+      </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
+    <row r="14" spans="1:19" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2026</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>239</v>
+      </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
+    <row r="15" spans="1:19" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2026</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="S15" s="6" t="s">
+        <v>256</v>
+      </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
+    <row r="16" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2020</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>272</v>
+      </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
+    <row r="17" spans="1:19" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2025</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="S20" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2026</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="S22" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2024</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="S24" s="7" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2025</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2026</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="S26" s="7" t="s">
+        <v>439</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S2" r:id="rId1" xr:uid="{A38B69B3-169A-4791-9FC8-7128EB513ACD}"/>
     <hyperlink ref="S3" r:id="rId2" xr:uid="{5751E136-023C-4145-B87C-091A39F7EC45}"/>
+    <hyperlink ref="S4" r:id="rId3" xr:uid="{15786666-2A92-4A2D-9BF5-779CF615DDC2}"/>
+    <hyperlink ref="S5" r:id="rId4" xr:uid="{E6EFD065-CB51-4D75-A194-44E45A32B826}"/>
+    <hyperlink ref="S6" r:id="rId5" xr:uid="{4A225668-A9C6-4B36-89A3-08A113112375}"/>
+    <hyperlink ref="S7" r:id="rId6" xr:uid="{2082D5E3-98EB-4859-B7CF-607E3F8E1FF4}"/>
+    <hyperlink ref="S8" r:id="rId7" xr:uid="{5DB59DAA-1631-49C4-A182-3A43C33B9D4B}"/>
+    <hyperlink ref="S9" r:id="rId8" xr:uid="{B87D4ADE-A9CA-4F8E-AF96-8EA2B1A4E0E6}"/>
+    <hyperlink ref="S10" r:id="rId9" xr:uid="{206113AA-04FC-4721-8A8F-44FE4D5EE61C}"/>
+    <hyperlink ref="S26" r:id="rId10" xr:uid="{41071F96-DB59-4432-A8F0-E23ABB369693}"/>
+    <hyperlink ref="S25" r:id="rId11" xr:uid="{7B85613B-44CD-41A9-B346-75C4423FCA03}"/>
+    <hyperlink ref="S24" r:id="rId12" xr:uid="{44CB87EC-C100-4EC6-A6B4-87D15B669C2C}"/>
+    <hyperlink ref="S23" r:id="rId13" xr:uid="{8CCE9181-8BD7-4803-9CCA-F5FFD32F7664}"/>
+    <hyperlink ref="S22" r:id="rId14" xr:uid="{8738D750-EF6E-41C2-992E-ED3D208AE96E}"/>
+    <hyperlink ref="S21" r:id="rId15" xr:uid="{FF343E17-6458-4A25-B064-1BE337E1CDF8}"/>
+    <hyperlink ref="S12" r:id="rId16" xr:uid="{E2787181-0AF8-409D-9CD7-CE61586794CF}"/>
+    <hyperlink ref="S13" r:id="rId17" xr:uid="{1A4C087D-8719-4A4E-AFEF-BC2B4AEBA3EC}"/>
+    <hyperlink ref="S14" r:id="rId18" xr:uid="{4E6225C6-E218-458D-ACF4-A68828527A40}"/>
+    <hyperlink ref="S15" r:id="rId19" xr:uid="{94C88D5F-CC86-4080-8251-3F97D546E343}"/>
+    <hyperlink ref="S16" r:id="rId20" xr:uid="{9FE88974-BBF8-4EDD-813D-3BB3C170D578}"/>
+    <hyperlink ref="S17" r:id="rId21" xr:uid="{A2D277B9-AA66-410F-8B16-8D599765DE78}"/>
+    <hyperlink ref="S18" r:id="rId22" xr:uid="{5504581A-D81E-448C-81B8-2C5E6C85BB4E}"/>
+    <hyperlink ref="S19" r:id="rId23" xr:uid="{7E01C0BB-A625-40D7-9DED-CEC04B97205A}"/>
+    <hyperlink ref="S20" r:id="rId24" xr:uid="{47C40677-F008-47EA-98C0-BF87217F3DC1}"/>
+    <hyperlink ref="S11" r:id="rId25" xr:uid="{DE00500F-69F7-474D-A8C5-E9E5A3B965D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>